--- a/source-excel/SALE.xlsx
+++ b/source-excel/SALE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\newstarrating\source-excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD0D0AB-4F1F-475D-9A09-6D6EA46DB204}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6026C054-2077-4052-8827-8C5FDB39350A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{51F89FC5-9E8B-4444-B8E4-5BD9F41461A1}"/>
   </bookViews>
@@ -6223,28 +6223,28 @@
         <v>21</v>
       </c>
       <c r="G55" s="11">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="H55" s="11">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="I55" s="11">
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="J55" s="11">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="K55" s="11">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="L55" s="11">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="M55" s="11">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="N55" s="11">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="O55" s="11">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="12">
-        <v>0</v>
+        <v>5373</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="17.5" thickBot="1" x14ac:dyDescent="0.65">
